--- a/veri.xlsx
+++ b/veri.xlsx
@@ -522,10 +522,10 @@
     <t>1.06.2026</t>
   </si>
   <si>
-    <t>1.05.2026</t>
-  </si>
-  <si>
     <t>1.06.2029</t>
+  </si>
+  <si>
+    <t>1.03.2028</t>
   </si>
 </sst>
 </file>
@@ -1046,7 +1046,7 @@
     </row>
     <row r="2" spans="1:8" s="3" customFormat="1" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>3</v>
@@ -1058,10 +1058,10 @@
         <v>144</v>
       </c>
       <c r="E2" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="F2" s="21" t="s">
         <v>160</v>
-      </c>
-      <c r="F2" s="21" t="s">
-        <v>161</v>
       </c>
       <c r="G2" s="18"/>
       <c r="H2" s="17"/>
@@ -5111,6 +5111,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6b2976ba-2c7f-4143-a057-6d51b0b96f16" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1299a56b-5065-46dd-9c72-8c4bb3604c63">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Belge" ma:contentTypeID="0x0101005F15455A22783E4A8D7CEE23BA64565F" ma:contentTypeVersion="13" ma:contentTypeDescription="Yeni belge oluşturun." ma:contentTypeScope="" ma:versionID="a5a17247843f064e67e5711b0f0a8dd6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1299a56b-5065-46dd-9c72-8c4bb3604c63" xmlns:ns3="6b2976ba-2c7f-4143-a057-6d51b0b96f16" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="323839205ccf02446c95c8b3c05b93ae" ns2:_="" ns3:_="">
     <xsd:import namespace="1299a56b-5065-46dd-9c72-8c4bb3604c63"/>
@@ -5317,41 +5337,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6b2976ba-2c7f-4143-a057-6d51b0b96f16" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1299a56b-5065-46dd-9c72-8c4bb3604c63">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{197E3A00-F4E5-4991-881A-B8CEB1B2A1F3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{612245CC-7D7F-479E-8816-D41693E15879}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="1299a56b-5065-46dd-9c72-8c4bb3604c63"/>
-    <ds:schemaRef ds:uri="6b2976ba-2c7f-4143-a057-6d51b0b96f16"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5374,9 +5363,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{612245CC-7D7F-479E-8816-D41693E15879}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{197E3A00-F4E5-4991-881A-B8CEB1B2A1F3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1299a56b-5065-46dd-9c72-8c4bb3604c63"/>
+    <ds:schemaRef ds:uri="6b2976ba-2c7f-4143-a057-6d51b0b96f16"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/veri.xlsx
+++ b/veri.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="159">
   <si>
     <t>TÜRÜ</t>
   </si>
@@ -517,15 +517,6 @@
   </si>
   <si>
     <t>1.08.2027</t>
-  </si>
-  <si>
-    <t>1.06.2026</t>
-  </si>
-  <si>
-    <t>1.06.2029</t>
-  </si>
-  <si>
-    <t>1.03.2028</t>
   </si>
 </sst>
 </file>
@@ -1058,10 +1049,10 @@
         <v>144</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="G2" s="18"/>
       <c r="H2" s="17"/>
@@ -1083,7 +1074,7 @@
         <v>147</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G3" s="19"/>
     </row>
@@ -1104,7 +1095,7 @@
         <v>148</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G4" s="20"/>
     </row>
@@ -1125,7 +1116,7 @@
         <v>148</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G5" s="20"/>
     </row>
@@ -1146,7 +1137,7 @@
         <v>147</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G6" s="20"/>
     </row>
@@ -1167,7 +1158,7 @@
         <v>147</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G7" s="20"/>
     </row>
@@ -1188,7 +1179,7 @@
         <v>149</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G8" s="20"/>
     </row>
@@ -1209,7 +1200,7 @@
         <v>149</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G9" s="20"/>
     </row>
@@ -1230,7 +1221,7 @@
         <v>150</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G10" s="20"/>
     </row>
@@ -1251,7 +1242,7 @@
         <v>151</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G11" s="20"/>
     </row>
@@ -1272,7 +1263,7 @@
         <v>147</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G12" s="20"/>
     </row>
@@ -1293,7 +1284,7 @@
         <v>149</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G13" s="20"/>
     </row>
@@ -1314,7 +1305,7 @@
         <v>149</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G14" s="20"/>
     </row>
@@ -1335,7 +1326,7 @@
         <v>151</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G15" s="20"/>
     </row>
@@ -1356,7 +1347,7 @@
         <v>149</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G16" s="20"/>
     </row>
@@ -1377,7 +1368,7 @@
         <v>147</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G17" s="20"/>
     </row>
@@ -1398,7 +1389,7 @@
         <v>148</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G18" s="20"/>
     </row>
@@ -1419,7 +1410,7 @@
         <v>148</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G19" s="20"/>
     </row>
@@ -1440,7 +1431,7 @@
         <v>148</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G20" s="20"/>
     </row>
@@ -1461,7 +1452,7 @@
         <v>148</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G21" s="20"/>
     </row>
@@ -1482,7 +1473,7 @@
         <v>152</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G22" s="20"/>
     </row>
@@ -1503,7 +1494,7 @@
         <v>152</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G23" s="20"/>
     </row>
@@ -1524,7 +1515,7 @@
         <v>151</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G24" s="20"/>
     </row>
@@ -1545,7 +1536,7 @@
         <v>147</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G25" s="20"/>
     </row>
@@ -1566,7 +1557,7 @@
         <v>147</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G26" s="20"/>
     </row>
@@ -1587,7 +1578,7 @@
         <v>147</v>
       </c>
       <c r="F27" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G27" s="20"/>
     </row>
@@ -1608,7 +1599,7 @@
         <v>147</v>
       </c>
       <c r="F28" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G28" s="20"/>
     </row>
@@ -1629,7 +1620,7 @@
         <v>147</v>
       </c>
       <c r="F29" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G29" s="20"/>
     </row>
@@ -1650,7 +1641,7 @@
         <v>147</v>
       </c>
       <c r="F30" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G30" s="20"/>
     </row>
@@ -1671,7 +1662,7 @@
         <v>147</v>
       </c>
       <c r="F31" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G31" s="20"/>
     </row>
@@ -1692,7 +1683,7 @@
         <v>146</v>
       </c>
       <c r="F32" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G32" s="20"/>
     </row>
@@ -1713,7 +1704,7 @@
         <v>150</v>
       </c>
       <c r="F33" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G33" s="20"/>
     </row>
@@ -1734,7 +1725,7 @@
         <v>147</v>
       </c>
       <c r="F34" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G34" s="20"/>
     </row>
@@ -1755,7 +1746,7 @@
         <v>146</v>
       </c>
       <c r="F35" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G35" s="20"/>
     </row>
@@ -1776,7 +1767,7 @@
         <v>149</v>
       </c>
       <c r="F36" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G36" s="20"/>
     </row>
@@ -1797,7 +1788,7 @@
         <v>147</v>
       </c>
       <c r="F37" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G37" s="20"/>
     </row>
@@ -1818,7 +1809,7 @@
         <v>152</v>
       </c>
       <c r="F38" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G38" s="20"/>
     </row>
@@ -1839,7 +1830,7 @@
         <v>152</v>
       </c>
       <c r="F39" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G39" s="20"/>
     </row>
@@ -1860,7 +1851,7 @@
         <v>152</v>
       </c>
       <c r="F40" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G40" s="20"/>
     </row>
@@ -1881,7 +1872,7 @@
         <v>147</v>
       </c>
       <c r="F41" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G41" s="20"/>
     </row>
@@ -1902,7 +1893,7 @@
         <v>149</v>
       </c>
       <c r="F42" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G42" s="20"/>
     </row>
@@ -1923,7 +1914,7 @@
         <v>152</v>
       </c>
       <c r="F43" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G43" s="20"/>
     </row>
@@ -1944,7 +1935,7 @@
         <v>152</v>
       </c>
       <c r="F44" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G44" s="20"/>
     </row>
@@ -1965,7 +1956,7 @@
         <v>149</v>
       </c>
       <c r="F45" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G45" s="20"/>
     </row>
@@ -1986,7 +1977,7 @@
         <v>149</v>
       </c>
       <c r="F46" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G46" s="20"/>
     </row>
@@ -2007,7 +1998,7 @@
         <v>149</v>
       </c>
       <c r="F47" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G47" s="20"/>
     </row>
@@ -2028,7 +2019,7 @@
         <v>153</v>
       </c>
       <c r="F48" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G48" s="20"/>
     </row>
@@ -2049,7 +2040,7 @@
         <v>152</v>
       </c>
       <c r="F49" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G49" s="20"/>
     </row>
@@ -2070,7 +2061,7 @@
         <v>149</v>
       </c>
       <c r="F50" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G50" s="20"/>
     </row>
@@ -2091,7 +2082,7 @@
         <v>147</v>
       </c>
       <c r="F51" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G51" s="20"/>
     </row>
@@ -2112,7 +2103,7 @@
         <v>152</v>
       </c>
       <c r="F52" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G52" s="20"/>
     </row>
@@ -2133,7 +2124,7 @@
         <v>149</v>
       </c>
       <c r="F53" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G53" s="20"/>
     </row>
@@ -2154,7 +2145,7 @@
         <v>147</v>
       </c>
       <c r="F54" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G54" s="20"/>
     </row>
@@ -2175,7 +2166,7 @@
         <v>154</v>
       </c>
       <c r="F55" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G55" s="20"/>
     </row>
@@ -2196,7 +2187,7 @@
         <v>152</v>
       </c>
       <c r="F56" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G56" s="20"/>
     </row>
@@ -2217,7 +2208,7 @@
         <v>152</v>
       </c>
       <c r="F57" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G57" s="20"/>
     </row>
@@ -2238,7 +2229,7 @@
         <v>155</v>
       </c>
       <c r="F58" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G58" s="20"/>
     </row>
@@ -2259,7 +2250,7 @@
         <v>152</v>
       </c>
       <c r="F59" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G59" s="20"/>
     </row>
@@ -2280,7 +2271,7 @@
         <v>152</v>
       </c>
       <c r="F60" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G60" s="20"/>
     </row>
@@ -2301,7 +2292,7 @@
         <v>152</v>
       </c>
       <c r="F61" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G61" s="20"/>
     </row>
@@ -2322,7 +2313,7 @@
         <v>149</v>
       </c>
       <c r="F62" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G62" s="20"/>
     </row>
@@ -2343,7 +2334,7 @@
         <v>149</v>
       </c>
       <c r="F63" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G63" s="20"/>
     </row>
@@ -2364,7 +2355,7 @@
         <v>152</v>
       </c>
       <c r="F64" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G64" s="20"/>
     </row>
@@ -2385,7 +2376,7 @@
         <v>152</v>
       </c>
       <c r="F65" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G65" s="20"/>
     </row>
@@ -2406,7 +2397,7 @@
         <v>152</v>
       </c>
       <c r="F66" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G66" s="20"/>
     </row>
@@ -2427,7 +2418,7 @@
         <v>147</v>
       </c>
       <c r="F67" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G67" s="20"/>
     </row>
@@ -2448,7 +2439,7 @@
         <v>152</v>
       </c>
       <c r="F68" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G68" s="20"/>
     </row>
@@ -2469,7 +2460,7 @@
         <v>147</v>
       </c>
       <c r="F69" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G69" s="20"/>
     </row>
@@ -2490,7 +2481,7 @@
         <v>149</v>
       </c>
       <c r="F70" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G70" s="20"/>
     </row>
@@ -2511,7 +2502,7 @@
         <v>149</v>
       </c>
       <c r="F71" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G71" s="20"/>
     </row>
@@ -2532,7 +2523,7 @@
         <v>149</v>
       </c>
       <c r="F72" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G72" s="20"/>
     </row>
@@ -2553,7 +2544,7 @@
         <v>146</v>
       </c>
       <c r="F73" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G73" s="20"/>
     </row>
@@ -2574,7 +2565,7 @@
         <v>152</v>
       </c>
       <c r="F74" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G74" s="20"/>
     </row>
@@ -2595,7 +2586,7 @@
         <v>152</v>
       </c>
       <c r="F75" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G75" s="20"/>
     </row>
@@ -2616,7 +2607,7 @@
         <v>150</v>
       </c>
       <c r="F76" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G76" s="20"/>
     </row>
@@ -2637,7 +2628,7 @@
         <v>152</v>
       </c>
       <c r="F77" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G77" s="20"/>
     </row>
@@ -2658,7 +2649,7 @@
         <v>154</v>
       </c>
       <c r="F78" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G78" s="20"/>
     </row>
@@ -2679,7 +2670,7 @@
         <v>151</v>
       </c>
       <c r="F79" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G79" s="20"/>
     </row>
@@ -2700,7 +2691,7 @@
         <v>151</v>
       </c>
       <c r="F80" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G80" s="20"/>
     </row>
@@ -2721,7 +2712,7 @@
         <v>152</v>
       </c>
       <c r="F81" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G81" s="20"/>
     </row>
@@ -2742,7 +2733,7 @@
         <v>151</v>
       </c>
       <c r="F82" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G82" s="16"/>
     </row>
@@ -2763,7 +2754,7 @@
         <v>147</v>
       </c>
       <c r="F83" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G83" s="20"/>
     </row>
@@ -2784,7 +2775,7 @@
         <v>147</v>
       </c>
       <c r="F84" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G84" s="20"/>
     </row>
@@ -2805,7 +2796,7 @@
         <v>147</v>
       </c>
       <c r="F85" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G85" s="20"/>
     </row>
@@ -2826,7 +2817,7 @@
         <v>149</v>
       </c>
       <c r="F86" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G86" s="20"/>
     </row>
@@ -2847,7 +2838,7 @@
         <v>149</v>
       </c>
       <c r="F87" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G87" s="20"/>
     </row>
@@ -2868,7 +2859,7 @@
         <v>149</v>
       </c>
       <c r="F88" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G88" s="20"/>
     </row>
@@ -2889,7 +2880,7 @@
         <v>155</v>
       </c>
       <c r="F89" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G89" s="20"/>
     </row>
@@ -2910,7 +2901,7 @@
         <v>155</v>
       </c>
       <c r="F90" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G90" s="20"/>
     </row>
@@ -2931,7 +2922,7 @@
         <v>149</v>
       </c>
       <c r="F91" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G91" s="20"/>
     </row>
@@ -2952,7 +2943,7 @@
         <v>150</v>
       </c>
       <c r="F92" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G92" s="20"/>
     </row>
@@ -2973,7 +2964,7 @@
         <v>146</v>
       </c>
       <c r="F93" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G93" s="20"/>
     </row>
@@ -2994,7 +2985,7 @@
         <v>152</v>
       </c>
       <c r="F94" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G94" s="20"/>
     </row>
@@ -3015,7 +3006,7 @@
         <v>151</v>
       </c>
       <c r="F95" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G95" s="20"/>
     </row>
@@ -3036,7 +3027,7 @@
         <v>150</v>
       </c>
       <c r="F96" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G96" s="20"/>
     </row>
@@ -3057,7 +3048,7 @@
         <v>147</v>
       </c>
       <c r="F97" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G97" s="16"/>
     </row>
@@ -3078,7 +3069,7 @@
         <v>147</v>
       </c>
       <c r="F98" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G98" s="20"/>
     </row>
@@ -3099,7 +3090,7 @@
         <v>151</v>
       </c>
       <c r="F99" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G99" s="20"/>
     </row>
@@ -3120,7 +3111,7 @@
         <v>151</v>
       </c>
       <c r="F100" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G100" s="20"/>
     </row>
@@ -3141,7 +3132,7 @@
         <v>156</v>
       </c>
       <c r="F101" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G101" s="20"/>
     </row>
@@ -3162,7 +3153,7 @@
         <v>156</v>
       </c>
       <c r="F102" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G102" s="20"/>
     </row>
@@ -3183,7 +3174,7 @@
         <v>156</v>
       </c>
       <c r="F103" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G103" s="20"/>
     </row>
@@ -3204,7 +3195,7 @@
         <v>147</v>
       </c>
       <c r="F104" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G104" s="20"/>
     </row>
@@ -3225,7 +3216,7 @@
         <v>147</v>
       </c>
       <c r="F105" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G105" s="20"/>
     </row>
@@ -3246,7 +3237,7 @@
         <v>157</v>
       </c>
       <c r="F106" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G106" s="20"/>
     </row>
@@ -3267,7 +3258,7 @@
         <v>147</v>
       </c>
       <c r="F107" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G107" s="20"/>
     </row>
@@ -3288,7 +3279,7 @@
         <v>152</v>
       </c>
       <c r="F108" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G108" s="20"/>
     </row>
@@ -3309,7 +3300,7 @@
         <v>155</v>
       </c>
       <c r="F109" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G109" s="20"/>
     </row>
@@ -3330,7 +3321,7 @@
         <v>147</v>
       </c>
       <c r="F110" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G110" s="20"/>
     </row>
@@ -3351,7 +3342,7 @@
         <v>147</v>
       </c>
       <c r="F111" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G111" s="20"/>
     </row>
@@ -3372,7 +3363,7 @@
         <v>146</v>
       </c>
       <c r="F112" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G112" s="20"/>
     </row>
@@ -3393,7 +3384,7 @@
         <v>148</v>
       </c>
       <c r="F113" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G113" s="20"/>
     </row>
@@ -3414,7 +3405,7 @@
         <v>152</v>
       </c>
       <c r="F114" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G114" s="20"/>
     </row>
@@ -3435,7 +3426,7 @@
         <v>149</v>
       </c>
       <c r="F115" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G115" s="20"/>
     </row>
@@ -3456,7 +3447,7 @@
         <v>150</v>
       </c>
       <c r="F116" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G116" s="20"/>
     </row>
@@ -3477,7 +3468,7 @@
         <v>147</v>
       </c>
       <c r="F117" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G117" s="20"/>
     </row>
@@ -3498,7 +3489,7 @@
         <v>146</v>
       </c>
       <c r="F118" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G118" s="20"/>
     </row>
@@ -3519,7 +3510,7 @@
         <v>146</v>
       </c>
       <c r="F119" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G119" s="20"/>
     </row>
@@ -3540,7 +3531,7 @@
         <v>149</v>
       </c>
       <c r="F120" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G120" s="20"/>
     </row>
@@ -3561,7 +3552,7 @@
         <v>158</v>
       </c>
       <c r="F121" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G121" s="20"/>
     </row>
@@ -3582,7 +3573,7 @@
         <v>158</v>
       </c>
       <c r="F122" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G122" s="20"/>
     </row>
@@ -3603,7 +3594,7 @@
         <v>158</v>
       </c>
       <c r="F123" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G123" s="20"/>
     </row>
@@ -3624,7 +3615,7 @@
         <v>149</v>
       </c>
       <c r="F124" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G124" s="20"/>
     </row>
@@ -3645,7 +3636,7 @@
         <v>149</v>
       </c>
       <c r="F125" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G125" s="20"/>
     </row>
@@ -3666,7 +3657,7 @@
         <v>148</v>
       </c>
       <c r="F126" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G126" s="20"/>
     </row>
@@ -3687,7 +3678,7 @@
         <v>151</v>
       </c>
       <c r="F127" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G127" s="20"/>
     </row>
@@ -3708,7 +3699,7 @@
         <v>156</v>
       </c>
       <c r="F128" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G128" s="20"/>
     </row>
@@ -3729,7 +3720,7 @@
         <v>151</v>
       </c>
       <c r="F129" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G129" s="20"/>
     </row>
@@ -3750,7 +3741,7 @@
         <v>147</v>
       </c>
       <c r="F130" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G130" s="20"/>
     </row>
@@ -3771,7 +3762,7 @@
         <v>147</v>
       </c>
       <c r="F131" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G131" s="20"/>
     </row>
@@ -3792,7 +3783,7 @@
         <v>148</v>
       </c>
       <c r="F132" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G132" s="20"/>
     </row>
@@ -3813,7 +3804,7 @@
         <v>148</v>
       </c>
       <c r="F133" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G133" s="20"/>
     </row>
@@ -3834,7 +3825,7 @@
         <v>152</v>
       </c>
       <c r="F134" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G134" s="20"/>
     </row>
@@ -3855,7 +3846,7 @@
         <v>152</v>
       </c>
       <c r="F135" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G135" s="20"/>
     </row>
@@ -3876,7 +3867,7 @@
         <v>147</v>
       </c>
       <c r="F136" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G136" s="20"/>
     </row>
@@ -3897,7 +3888,7 @@
         <v>152</v>
       </c>
       <c r="F137" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G137" s="20"/>
     </row>
@@ -3918,7 +3909,7 @@
         <v>151</v>
       </c>
       <c r="F138" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G138" s="20"/>
     </row>
@@ -3939,7 +3930,7 @@
         <v>147</v>
       </c>
       <c r="F139" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G139" s="20"/>
     </row>
@@ -3960,7 +3951,7 @@
         <v>152</v>
       </c>
       <c r="F140" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G140" s="20"/>
     </row>
@@ -3981,7 +3972,7 @@
         <v>148</v>
       </c>
       <c r="F141" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G141" s="20"/>
     </row>
@@ -4002,7 +3993,7 @@
         <v>151</v>
       </c>
       <c r="F142" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G142" s="20"/>
     </row>
@@ -4023,7 +4014,7 @@
         <v>149</v>
       </c>
       <c r="F143" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G143" s="20"/>
     </row>
@@ -4044,7 +4035,7 @@
         <v>151</v>
       </c>
       <c r="F144" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G144" s="20"/>
     </row>
@@ -4065,7 +4056,7 @@
         <v>147</v>
       </c>
       <c r="F145" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G145" s="20"/>
     </row>
@@ -4086,7 +4077,7 @@
         <v>152</v>
       </c>
       <c r="F146" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G146" s="20"/>
     </row>
@@ -4107,7 +4098,7 @@
         <v>149</v>
       </c>
       <c r="F147" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G147" s="20"/>
     </row>
@@ -4128,7 +4119,7 @@
         <v>148</v>
       </c>
       <c r="F148" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G148" s="20"/>
     </row>
@@ -4149,7 +4140,7 @@
         <v>147</v>
       </c>
       <c r="F149" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G149" s="20"/>
     </row>
@@ -4170,7 +4161,7 @@
         <v>149</v>
       </c>
       <c r="F150" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G150" s="20"/>
     </row>
@@ -4191,7 +4182,7 @@
         <v>149</v>
       </c>
       <c r="F151" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G151" s="20"/>
     </row>
@@ -4212,7 +4203,7 @@
         <v>152</v>
       </c>
       <c r="F152" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G152" s="20"/>
     </row>
@@ -4233,7 +4224,7 @@
         <v>149</v>
       </c>
       <c r="F153" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G153" s="20"/>
     </row>
@@ -4254,7 +4245,7 @@
         <v>147</v>
       </c>
       <c r="F154" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G154" s="20"/>
     </row>
@@ -4275,7 +4266,7 @@
         <v>149</v>
       </c>
       <c r="F155" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G155" s="20"/>
     </row>
@@ -4296,7 +4287,7 @@
         <v>147</v>
       </c>
       <c r="F156" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G156" s="20"/>
     </row>
@@ -4317,7 +4308,7 @@
         <v>152</v>
       </c>
       <c r="F157" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G157" s="20"/>
     </row>
@@ -4338,7 +4329,7 @@
         <v>147</v>
       </c>
       <c r="F158" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G158" s="20"/>
     </row>
@@ -4359,7 +4350,7 @@
         <v>148</v>
       </c>
       <c r="F159" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G159" s="20"/>
     </row>
@@ -4380,7 +4371,7 @@
         <v>147</v>
       </c>
       <c r="F160" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G160" s="20"/>
     </row>
@@ -4401,7 +4392,7 @@
         <v>151</v>
       </c>
       <c r="F161" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G161" s="20"/>
     </row>
@@ -4422,7 +4413,7 @@
         <v>152</v>
       </c>
       <c r="F162" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G162" s="20"/>
     </row>
@@ -4443,7 +4434,7 @@
         <v>148</v>
       </c>
       <c r="F163" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G163" s="20"/>
     </row>
@@ -4464,7 +4455,7 @@
         <v>151</v>
       </c>
       <c r="F164" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G164" s="20"/>
     </row>
@@ -4485,7 +4476,7 @@
         <v>148</v>
       </c>
       <c r="F165" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G165" s="20"/>
     </row>
@@ -4506,7 +4497,7 @@
         <v>147</v>
       </c>
       <c r="F166" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G166" s="20"/>
     </row>
@@ -4527,7 +4518,7 @@
         <v>147</v>
       </c>
       <c r="F167" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G167" s="20"/>
     </row>
@@ -4548,7 +4539,7 @@
         <v>147</v>
       </c>
       <c r="F168" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G168" s="20"/>
     </row>
@@ -4569,7 +4560,7 @@
         <v>147</v>
       </c>
       <c r="F169" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G169" s="20"/>
     </row>
@@ -4590,7 +4581,7 @@
         <v>152</v>
       </c>
       <c r="F170" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G170" s="20"/>
     </row>
@@ -4611,7 +4602,7 @@
         <v>152</v>
       </c>
       <c r="F171" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G171" s="20"/>
     </row>
@@ -4632,7 +4623,7 @@
         <v>147</v>
       </c>
       <c r="F172" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G172" s="20"/>
     </row>
@@ -4653,7 +4644,7 @@
         <v>151</v>
       </c>
       <c r="F173" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G173" s="20"/>
     </row>
@@ -4674,7 +4665,7 @@
         <v>148</v>
       </c>
       <c r="F174" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G174" s="20"/>
     </row>
@@ -4695,7 +4686,7 @@
         <v>151</v>
       </c>
       <c r="F175" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G175" s="20"/>
     </row>
@@ -4716,7 +4707,7 @@
         <v>146</v>
       </c>
       <c r="F176" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G176" s="20"/>
     </row>
@@ -4737,7 +4728,7 @@
         <v>152</v>
       </c>
       <c r="F177" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G177" s="20"/>
     </row>
@@ -4758,7 +4749,7 @@
         <v>152</v>
       </c>
       <c r="F178" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G178" s="20"/>
     </row>
@@ -4779,7 +4770,7 @@
         <v>148</v>
       </c>
       <c r="F179" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G179" s="20"/>
     </row>
@@ -4800,7 +4791,7 @@
         <v>147</v>
       </c>
       <c r="F180" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G180" s="20"/>
     </row>
@@ -4821,7 +4812,7 @@
         <v>152</v>
       </c>
       <c r="F181" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G181" s="20"/>
     </row>
@@ -4842,7 +4833,7 @@
         <v>151</v>
       </c>
       <c r="F182" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G182" s="20"/>
     </row>
@@ -4863,7 +4854,7 @@
         <v>152</v>
       </c>
       <c r="F183" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G183" s="20"/>
     </row>
@@ -4884,7 +4875,7 @@
         <v>152</v>
       </c>
       <c r="F184" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G184" s="20"/>
     </row>
@@ -4905,7 +4896,7 @@
         <v>150</v>
       </c>
       <c r="F185" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G185" s="20"/>
     </row>
@@ -4926,7 +4917,7 @@
         <v>150</v>
       </c>
       <c r="F186" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G186" s="20"/>
     </row>
@@ -4947,7 +4938,7 @@
         <v>157</v>
       </c>
       <c r="F187" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G187" s="20"/>
     </row>
@@ -4968,7 +4959,7 @@
         <v>152</v>
       </c>
       <c r="F188" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G188" s="20"/>
     </row>
@@ -4989,7 +4980,7 @@
         <v>151</v>
       </c>
       <c r="F189" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G189" s="20"/>
     </row>
@@ -5010,7 +5001,7 @@
         <v>148</v>
       </c>
       <c r="F190" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G190" s="20"/>
     </row>
@@ -5031,7 +5022,7 @@
         <v>151</v>
       </c>
       <c r="F191" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G191" s="20"/>
     </row>
@@ -5052,7 +5043,7 @@
         <v>151</v>
       </c>
       <c r="F192" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G192" s="20"/>
     </row>
@@ -5073,7 +5064,7 @@
         <v>151</v>
       </c>
       <c r="F193" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G193" s="20"/>
     </row>
@@ -5094,7 +5085,7 @@
         <v>151</v>
       </c>
       <c r="F194" s="21" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G194" s="20"/>
     </row>
@@ -5120,17 +5111,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6b2976ba-2c7f-4143-a057-6d51b0b96f16" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1299a56b-5065-46dd-9c72-8c4bb3604c63">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Belge" ma:contentTypeID="0x0101005F15455A22783E4A8D7CEE23BA64565F" ma:contentTypeVersion="13" ma:contentTypeDescription="Yeni belge oluşturun." ma:contentTypeScope="" ma:versionID="a5a17247843f064e67e5711b0f0a8dd6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1299a56b-5065-46dd-9c72-8c4bb3604c63" xmlns:ns3="6b2976ba-2c7f-4143-a057-6d51b0b96f16" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="323839205ccf02446c95c8b3c05b93ae" ns2:_="" ns3:_="">
     <xsd:import namespace="1299a56b-5065-46dd-9c72-8c4bb3604c63"/>
@@ -5337,6 +5317,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6b2976ba-2c7f-4143-a057-6d51b0b96f16" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1299a56b-5065-46dd-9c72-8c4bb3604c63">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{612245CC-7D7F-479E-8816-D41693E15879}">
   <ds:schemaRefs>
@@ -5346,23 +5337,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB05B24D-6AF9-4354-A5AA-C593A88E8E42}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1299a56b-5065-46dd-9c72-8c4bb3604c63"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="6b2976ba-2c7f-4143-a057-6d51b0b96f16"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{197E3A00-F4E5-4991-881A-B8CEB1B2A1F3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5379,4 +5353,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB05B24D-6AF9-4354-A5AA-C593A88E8E42}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1299a56b-5065-46dd-9c72-8c4bb3604c63"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="6b2976ba-2c7f-4143-a057-6d51b0b96f16"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>